--- a/CCF2026.xlsx
+++ b/CCF2026.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="3">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="4">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="5">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="6">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="7">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="9">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="11">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="13">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="14">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="16">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="18">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="20">
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="21">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="23">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="24">
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="25">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="26">
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="27">
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="28">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="29">
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="30">
@@ -4151,7 +4151,7 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="98">
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="99">
@@ -4230,9 +4230,7 @@
           <t>http://dblp.uni-trier.de/db/journals/ton/</t>
         </is>
       </c>
-      <c r="H99" t="n">
-        <v>3.6</v>
-      </c>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4271,7 +4269,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="101">
@@ -4311,7 +4309,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="102">
@@ -4391,7 +4389,7 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="104">
@@ -4431,7 +4429,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="105">
@@ -4471,7 +4469,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="106">
@@ -4511,7 +4509,7 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="107">
@@ -4551,7 +4549,7 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="108">
@@ -4591,7 +4589,7 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="109">
@@ -4671,7 +4669,7 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="111">
@@ -4711,7 +4709,7 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="112">
@@ -4751,7 +4749,7 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -4791,7 +4789,7 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="114">
@@ -4869,7 +4867,7 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="116">
@@ -4909,7 +4907,7 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -4949,7 +4947,7 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="118">
@@ -6281,7 +6279,7 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="153">
@@ -6321,7 +6319,7 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="154">
@@ -6361,7 +6359,7 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="155">
@@ -6401,7 +6399,7 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156">
@@ -6441,7 +6439,7 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="157">
@@ -6561,7 +6559,7 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="160">
@@ -6601,7 +6599,7 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="161">
@@ -6681,7 +6679,7 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -6721,7 +6719,7 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="164">
@@ -6841,7 +6839,7 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="167">
@@ -6919,7 +6917,7 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="169">
@@ -8099,7 +8097,7 @@
         </is>
       </c>
       <c r="H199" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="200">
@@ -8139,7 +8137,7 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="201">
@@ -8179,7 +8177,7 @@
         </is>
       </c>
       <c r="H201" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="202">
@@ -8219,7 +8217,7 @@
         </is>
       </c>
       <c r="H202" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="203">
@@ -8259,7 +8257,7 @@
         </is>
       </c>
       <c r="H203" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="204">
@@ -8299,7 +8297,7 @@
         </is>
       </c>
       <c r="H204" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="205">
@@ -8339,7 +8337,7 @@
         </is>
       </c>
       <c r="H205" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="206">
@@ -8379,7 +8377,7 @@
         </is>
       </c>
       <c r="H206" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="207">
@@ -8419,7 +8417,7 @@
         </is>
       </c>
       <c r="H207" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
@@ -8459,7 +8457,7 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="209">
@@ -8499,7 +8497,7 @@
         </is>
       </c>
       <c r="H209" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="210">
@@ -8579,7 +8577,7 @@
         </is>
       </c>
       <c r="H211" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="212">
@@ -8619,7 +8617,7 @@
         </is>
       </c>
       <c r="H212" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213">
@@ -8659,7 +8657,7 @@
         </is>
       </c>
       <c r="H213" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="214">
@@ -8699,7 +8697,7 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="215">
@@ -8777,7 +8775,7 @@
         </is>
       </c>
       <c r="H216" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -8817,7 +8815,7 @@
         </is>
       </c>
       <c r="H217" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="218">
@@ -8857,7 +8855,7 @@
         </is>
       </c>
       <c r="H218" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
@@ -8897,7 +8895,7 @@
         </is>
       </c>
       <c r="H219" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="220">
@@ -8937,7 +8935,7 @@
         </is>
       </c>
       <c r="H220" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221">
@@ -8977,7 +8975,7 @@
         </is>
       </c>
       <c r="H221" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="222">
@@ -9017,7 +9015,7 @@
         </is>
       </c>
       <c r="H222" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="223">
@@ -9057,7 +9055,7 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="224">
@@ -10731,7 +10729,7 @@
         </is>
       </c>
       <c r="H267" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
@@ -11265,7 +11263,7 @@
         </is>
       </c>
       <c r="H281" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="282">
@@ -11305,7 +11303,7 @@
         </is>
       </c>
       <c r="H282" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="283">
@@ -11345,7 +11343,7 @@
         </is>
       </c>
       <c r="H283" t="n">
-        <v>10.4</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="284">
@@ -11423,7 +11421,7 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>4.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="286">
@@ -11463,7 +11461,7 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="287">
@@ -11503,7 +11501,7 @@
         </is>
       </c>
       <c r="H287" t="n">
-        <v>9.9</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="288">
@@ -11543,7 +11541,7 @@
         </is>
       </c>
       <c r="H288" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="289">
@@ -11583,7 +11581,7 @@
         </is>
       </c>
       <c r="H289" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="290">
@@ -11623,7 +11621,7 @@
         </is>
       </c>
       <c r="H290" t="n">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="291">
@@ -11663,7 +11661,7 @@
         </is>
       </c>
       <c r="H291" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="292">
@@ -11703,7 +11701,7 @@
         </is>
       </c>
       <c r="H292" t="n">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="293">
@@ -11743,7 +11741,7 @@
         </is>
       </c>
       <c r="H293" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="294">
@@ -11783,7 +11781,7 @@
         </is>
       </c>
       <c r="H294" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="295">
@@ -11823,7 +11821,7 @@
         </is>
       </c>
       <c r="H295" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="296">
@@ -11863,7 +11861,7 @@
         </is>
       </c>
       <c r="H296" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="297">
@@ -11903,7 +11901,7 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="298">
@@ -11943,7 +11941,7 @@
         </is>
       </c>
       <c r="H298" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="299">
@@ -11983,7 +11981,7 @@
         </is>
       </c>
       <c r="H299" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="300">
@@ -12023,7 +12021,7 @@
         </is>
       </c>
       <c r="H300" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
     </row>
     <row r="301">
@@ -12183,7 +12181,7 @@
         </is>
       </c>
       <c r="H304" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="305">
@@ -12223,7 +12221,7 @@
         </is>
       </c>
       <c r="H305" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="306">
@@ -12263,7 +12261,7 @@
         </is>
       </c>
       <c r="H306" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="307">
@@ -12302,9 +12300,7 @@
           <t>http://dblp.uni-trier.de/db/journals/ijswis/</t>
         </is>
       </c>
-      <c r="H307" t="n">
-        <v>5.6</v>
-      </c>
+      <c r="H307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -12343,7 +12339,7 @@
         </is>
       </c>
       <c r="H308" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="309">
@@ -12423,7 +12419,7 @@
         </is>
       </c>
       <c r="H310" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="311">
@@ -12463,7 +12459,7 @@
         </is>
       </c>
       <c r="H311" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="312">
@@ -12503,7 +12499,7 @@
         </is>
       </c>
       <c r="H312" t="n">
-        <v>11.8</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="313">
@@ -12543,7 +12539,7 @@
         </is>
       </c>
       <c r="H313" t="n">
-        <v>6.6</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="314">
@@ -13799,7 +13795,7 @@
         </is>
       </c>
       <c r="H346" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="347">
@@ -13839,7 +13835,7 @@
         </is>
       </c>
       <c r="H347" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="348">
@@ -13879,7 +13875,7 @@
         </is>
       </c>
       <c r="H348" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="349">
@@ -13959,7 +13955,7 @@
         </is>
       </c>
       <c r="H350" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="351">
@@ -13999,7 +13995,7 @@
         </is>
       </c>
       <c r="H351" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="352">
@@ -14079,7 +14075,7 @@
         </is>
       </c>
       <c r="H353" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="354">
@@ -14119,7 +14115,7 @@
         </is>
       </c>
       <c r="H354" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="355">
@@ -14199,7 +14195,7 @@
         </is>
       </c>
       <c r="H356" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="357">
@@ -14279,7 +14275,7 @@
         </is>
       </c>
       <c r="H358" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="359">
@@ -14319,7 +14315,7 @@
         </is>
       </c>
       <c r="H359" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="360">
@@ -14399,7 +14395,7 @@
         </is>
       </c>
       <c r="H361" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="362">
@@ -14439,7 +14435,7 @@
         </is>
       </c>
       <c r="H362" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="363">
@@ -14558,9 +14554,7 @@
           <t>http://dblp.uni-trier.de/db/journals/fuin/</t>
         </is>
       </c>
-      <c r="H365" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="H365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -14639,7 +14633,7 @@
         </is>
       </c>
       <c r="H367" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="368">
@@ -14759,7 +14753,7 @@
         </is>
       </c>
       <c r="H370" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="371">
@@ -14839,7 +14833,7 @@
         </is>
       </c>
       <c r="H372" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="373">
@@ -14879,7 +14873,7 @@
         </is>
       </c>
       <c r="H373" t="n">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="374">
@@ -15869,7 +15863,7 @@
         </is>
       </c>
       <c r="H399" t="n">
-        <v>9.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="400">
@@ -15909,7 +15903,7 @@
         </is>
       </c>
       <c r="H400" t="n">
-        <v>13.7</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="401">
@@ -15949,7 +15943,7 @@
         </is>
       </c>
       <c r="H401" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="402">
@@ -15989,7 +15983,7 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="403">
@@ -16029,7 +16023,7 @@
         </is>
       </c>
       <c r="H403" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="404">
@@ -16109,7 +16103,7 @@
         </is>
       </c>
       <c r="H405" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="406">
@@ -16149,7 +16143,7 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="407">
@@ -16189,7 +16183,7 @@
         </is>
       </c>
       <c r="H407" t="n">
-        <v>11.1</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="408">
@@ -16229,7 +16223,7 @@
         </is>
       </c>
       <c r="H408" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="409">
@@ -16269,7 +16263,7 @@
         </is>
       </c>
       <c r="H409" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="410">
@@ -16309,7 +16303,7 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="411">
@@ -16349,7 +16343,7 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>18.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="412">
@@ -16429,7 +16423,7 @@
         </is>
       </c>
       <c r="H413" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="414">
@@ -16469,7 +16463,7 @@
         </is>
       </c>
       <c r="H414" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="415">
@@ -16509,7 +16503,7 @@
         </is>
       </c>
       <c r="H415" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="416">
@@ -16549,7 +16543,7 @@
         </is>
       </c>
       <c r="H416" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="417">
@@ -16589,7 +16583,7 @@
         </is>
       </c>
       <c r="H417" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="418">
@@ -16629,7 +16623,7 @@
         </is>
       </c>
       <c r="H418" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="419">
@@ -16669,7 +16663,7 @@
         </is>
       </c>
       <c r="H419" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="420">
@@ -16747,7 +16741,7 @@
         </is>
       </c>
       <c r="H421" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="422">
@@ -16787,7 +16781,7 @@
         </is>
       </c>
       <c r="H422" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="423">
@@ -16865,7 +16859,7 @@
         </is>
       </c>
       <c r="H424" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="425">
@@ -16945,7 +16939,7 @@
         </is>
       </c>
       <c r="H426" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="427">
@@ -18087,7 +18081,7 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>18.3</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="457">
@@ -18317,7 +18311,7 @@
         </is>
       </c>
       <c r="H462" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="463">
@@ -18357,7 +18351,7 @@
         </is>
       </c>
       <c r="H463" t="n">
-        <v>18.6</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="464">
@@ -18397,7 +18391,7 @@
         </is>
       </c>
       <c r="H464" t="n">
-        <v>9.300000000000001</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="465">
@@ -18437,7 +18431,7 @@
         </is>
       </c>
       <c r="H465" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="466">
@@ -18477,7 +18471,7 @@
         </is>
       </c>
       <c r="H466" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="467">
@@ -18517,7 +18511,7 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="468">
@@ -18557,7 +18551,7 @@
         </is>
       </c>
       <c r="H468" t="n">
-        <v>5.3</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="469">
@@ -18597,7 +18591,7 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="470">
@@ -18637,7 +18631,7 @@
         </is>
       </c>
       <c r="H470" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="471">
@@ -18677,7 +18671,7 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="472">
@@ -18717,7 +18711,7 @@
         </is>
       </c>
       <c r="H472" t="n">
-        <v>9.800000000000001</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="473">
@@ -18756,9 +18750,7 @@
           <t>http://dblp.uni-trier.de/db/journals/taslp/</t>
         </is>
       </c>
-      <c r="H473" t="n">
-        <v>5.1</v>
-      </c>
+      <c r="H473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -18797,7 +18789,7 @@
         </is>
       </c>
       <c r="H474" t="n">
-        <v>10.5</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="475">
@@ -18837,7 +18829,7 @@
         </is>
       </c>
       <c r="H475" t="n">
-        <v>12</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="476">
@@ -18877,7 +18869,7 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>11.9</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="477">
@@ -18917,7 +18909,7 @@
         </is>
       </c>
       <c r="H477" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="478">
@@ -18957,7 +18949,7 @@
         </is>
       </c>
       <c r="H478" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="479">
@@ -19115,7 +19107,7 @@
         </is>
       </c>
       <c r="H482" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="483">
@@ -19195,7 +19187,7 @@
         </is>
       </c>
       <c r="H484" t="n">
-        <v>6.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="485">
@@ -19235,7 +19227,7 @@
         </is>
       </c>
       <c r="H485" t="n">
-        <v>7.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="486">
@@ -19275,7 +19267,7 @@
         </is>
       </c>
       <c r="H486" t="n">
-        <v>6.9</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="487">
@@ -19315,7 +19307,7 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="488">
@@ -19395,7 +19387,7 @@
         </is>
       </c>
       <c r="H489" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="490">
@@ -19435,7 +19427,7 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="491">
@@ -19475,7 +19467,7 @@
         </is>
       </c>
       <c r="H491" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="492">
@@ -19515,7 +19507,7 @@
         </is>
       </c>
       <c r="H492" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -19555,7 +19547,7 @@
         </is>
       </c>
       <c r="H493" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="494">
@@ -19595,7 +19587,7 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="495">
@@ -19635,7 +19627,7 @@
         </is>
       </c>
       <c r="H495" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="496">
@@ -19675,7 +19667,7 @@
         </is>
       </c>
       <c r="H496" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="497">
@@ -19715,7 +19707,7 @@
         </is>
       </c>
       <c r="H497" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="498">
@@ -19755,7 +19747,7 @@
         </is>
       </c>
       <c r="H498" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="499">
@@ -19795,7 +19787,7 @@
         </is>
       </c>
       <c r="H499" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="500">
@@ -19835,7 +19827,7 @@
         </is>
       </c>
       <c r="H500" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="501">
@@ -19915,7 +19907,7 @@
         </is>
       </c>
       <c r="H502" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="503">
@@ -19995,7 +19987,7 @@
         </is>
       </c>
       <c r="H504" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="505">
@@ -20035,7 +20027,7 @@
         </is>
       </c>
       <c r="H505" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="506">
@@ -20075,7 +20067,7 @@
         </is>
       </c>
       <c r="H506" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="507">
@@ -20115,7 +20107,7 @@
         </is>
       </c>
       <c r="H507" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="508">
@@ -20195,7 +20187,7 @@
         </is>
       </c>
       <c r="H509" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="510">
@@ -20235,7 +20227,7 @@
         </is>
       </c>
       <c r="H510" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="511">
@@ -20275,7 +20267,7 @@
         </is>
       </c>
       <c r="H511" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="512">
@@ -20353,7 +20345,7 @@
         </is>
       </c>
       <c r="H513" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="514">
@@ -20393,7 +20385,7 @@
         </is>
       </c>
       <c r="H514" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="515">
@@ -20433,7 +20425,7 @@
         </is>
       </c>
       <c r="H515" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="516">
@@ -20551,7 +20543,7 @@
         </is>
       </c>
       <c r="H518" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="519">
@@ -20591,7 +20583,7 @@
         </is>
       </c>
       <c r="H519" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="520">
@@ -20631,7 +20623,7 @@
         </is>
       </c>
       <c r="H520" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="521">
@@ -20670,9 +20662,7 @@
           <t>http://dblp.uni-trier.de/db/journals/soco/</t>
         </is>
       </c>
-      <c r="H521" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="H521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -20711,7 +20701,7 @@
         </is>
       </c>
       <c r="H522" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="523">
@@ -20751,7 +20741,7 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="524">
@@ -22117,7 +22107,7 @@
         </is>
       </c>
       <c r="H559" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="560">
@@ -22499,7 +22489,7 @@
         </is>
       </c>
       <c r="H569" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="570">
@@ -22539,7 +22529,7 @@
         </is>
       </c>
       <c r="H570" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="571">
@@ -22617,7 +22607,7 @@
         </is>
       </c>
       <c r="H572" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="573">
@@ -22697,7 +22687,7 @@
         </is>
       </c>
       <c r="H574" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="575">
@@ -22737,7 +22727,7 @@
         </is>
       </c>
       <c r="H575" t="n">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="576">
@@ -22777,7 +22767,7 @@
         </is>
       </c>
       <c r="H576" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="577">
@@ -22817,7 +22807,7 @@
         </is>
       </c>
       <c r="H577" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="578">
@@ -22857,7 +22847,7 @@
         </is>
       </c>
       <c r="H578" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="579">
@@ -22897,7 +22887,7 @@
         </is>
       </c>
       <c r="H579" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="580">
@@ -22975,7 +22965,7 @@
         </is>
       </c>
       <c r="H581" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="582">
@@ -23055,7 +23045,7 @@
         </is>
       </c>
       <c r="H583" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="584">
